--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_001.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_001.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="186">
   <si>
     <t>Sezione</t>
   </si>
@@ -369,6 +369,12 @@
   </si>
   <si>
     <t>flagFirmatario</t>
+  </si>
+  <si>
+    <t>Età(anni)</t>
+  </si>
+  <si>
+    <t>anni</t>
   </si>
   <si>
     <t>Provincia AIRE</t>
@@ -622,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.76953125" customWidth="true" bestFit="true"/>
@@ -1424,7 +1430,7 @@
         <v>76</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>64</v>
@@ -2039,19 +2045,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C62" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -2062,19 +2068,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2085,19 +2091,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2108,19 +2114,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2131,19 +2137,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2154,19 +2160,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2177,19 +2183,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2200,19 +2206,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
@@ -2223,19 +2229,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2246,19 +2252,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2269,19 +2275,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -2292,19 +2298,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
@@ -2315,19 +2321,19 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2338,19 +2344,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
@@ -2361,19 +2367,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2384,19 +2390,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2407,19 +2413,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
@@ -2430,19 +2436,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2453,19 +2459,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2476,19 +2482,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
@@ -2499,19 +2505,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
@@ -2522,19 +2528,19 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
@@ -2545,19 +2551,19 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
@@ -2568,19 +2574,19 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
@@ -2591,19 +2597,19 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
@@ -2614,19 +2620,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -2637,19 +2643,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
@@ -2660,19 +2666,19 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
@@ -2683,19 +2689,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
@@ -2706,19 +2712,19 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
@@ -2729,19 +2735,19 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
@@ -2752,19 +2758,19 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
@@ -2775,19 +2781,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
@@ -2801,16 +2807,16 @@
         <v>131</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="E95" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
@@ -2824,16 +2830,16 @@
         <v>131</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
@@ -2844,19 +2850,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2867,19 +2873,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2890,19 +2896,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2913,19 +2919,19 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
@@ -2936,19 +2942,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
@@ -2959,19 +2965,19 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -2982,19 +2988,19 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -3005,19 +3011,19 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -3028,19 +3034,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>152</v>
+        <v>31</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -3051,19 +3057,19 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -3074,19 +3080,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -3097,19 +3103,19 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>10</v>
@@ -3120,19 +3126,19 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="C109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D109" s="2" t="s">
+      <c r="E109" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>10</v>
@@ -3143,19 +3149,19 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
@@ -3166,19 +3172,19 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
@@ -3189,19 +3195,19 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
@@ -3212,19 +3218,19 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
@@ -3235,19 +3241,19 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
@@ -3258,19 +3264,19 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
@@ -3281,19 +3287,19 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3304,19 +3310,19 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B117" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
@@ -3327,19 +3333,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>152</v>
+        <v>31</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
@@ -3350,19 +3356,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
@@ -3373,19 +3379,19 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
@@ -3399,19 +3405,19 @@
         <v>159</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="E121" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>29</v>
@@ -3422,16 +3428,16 @@
         <v>159</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>63</v>
+        <v>157</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>10</v>
@@ -3442,22 +3448,22 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>66</v>
+        <v>162</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>29</v>
@@ -3465,19 +3471,19 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
@@ -3488,22 +3494,22 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>29</v>
@@ -3511,19 +3517,19 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>10</v>
@@ -3534,19 +3540,19 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>22</v>
@@ -3557,22 +3563,22 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>29</v>
@@ -3580,22 +3586,22 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>29</v>
@@ -3603,22 +3609,22 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>29</v>
@@ -3626,19 +3632,19 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>10</v>
@@ -3649,22 +3655,22 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>29</v>
@@ -3672,19 +3678,19 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
@@ -3695,19 +3701,19 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>22</v>
@@ -3718,22 +3724,22 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>29</v>
@@ -3741,22 +3747,22 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>29</v>
@@ -3764,22 +3770,22 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>29</v>
@@ -3787,22 +3793,22 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>29</v>
@@ -3810,22 +3816,22 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>29</v>
@@ -3833,22 +3839,22 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>29</v>
@@ -3856,19 +3862,19 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>22</v>
@@ -3879,19 +3885,19 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>10</v>
@@ -3902,19 +3908,19 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>22</v>
@@ -3925,19 +3931,19 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>10</v>
@@ -3948,19 +3954,19 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>22</v>
@@ -3971,22 +3977,22 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>29</v>
@@ -3994,22 +4000,22 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>29</v>
@@ -4017,22 +4023,22 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>29</v>
@@ -4040,22 +4046,22 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B149" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D149" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="E149" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>29</v>
@@ -4063,19 +4069,19 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>10</v>
@@ -4086,22 +4092,22 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>29</v>
@@ -4109,19 +4115,19 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>10</v>
@@ -4132,19 +4138,19 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>10</v>
@@ -4155,19 +4161,19 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>10</v>
@@ -4178,19 +4184,19 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F155" s="2" t="s">
         <v>10</v>
@@ -4201,19 +4207,19 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>10</v>
@@ -4224,19 +4230,19 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>10</v>
@@ -4247,19 +4253,19 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>10</v>
@@ -4270,24 +4276,70 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B161" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E159" s="2" t="s">
+      <c r="C161" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F159" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G159" s="2" t="s">
+      <c r="F161" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G161" s="2" t="s">
         <v>29</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_001.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Matr_001.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="190">
   <si>
     <t>Sezione</t>
   </si>
@@ -125,10 +125,22 @@
     <t>Dati generali</t>
   </si>
   <si>
+    <t>Formato Data Evento Matrimonio</t>
+  </si>
+  <si>
+    <t>evento.datiEventoMatrimonio</t>
+  </si>
+  <si>
+    <t>idFormatoDataEvento</t>
+  </si>
+  <si>
+    <t>Formato Data Evento Matrimonio - Descrizione</t>
+  </si>
+  <si>
+    <t>formatoDataEvento</t>
+  </si>
+  <si>
     <t>Data Evento Matrimonio</t>
-  </si>
-  <si>
-    <t>evento.datiEventoMatrimonio</t>
   </si>
   <si>
     <t>dataEvento</t>
@@ -628,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="24.76953125" customWidth="true" bestFit="true"/>
@@ -1039,7 +1051,7 @@
         <v>37</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>38</v>
@@ -1062,13 +1074,13 @@
         <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
@@ -1082,16 +1094,16 @@
         <v>36</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -1105,13 +1117,13 @@
         <v>36</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>46</v>
@@ -1134,7 +1146,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>48</v>
@@ -1157,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>50</v>
@@ -1180,7 +1192,7 @@
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>52</v>
@@ -1203,7 +1215,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>54</v>
@@ -1223,13 +1235,13 @@
         <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>10</v>
@@ -1243,16 +1255,16 @@
         <v>36</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
@@ -1266,13 +1278,13 @@
         <v>36</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>61</v>
@@ -1286,19 +1298,19 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>10</v>
@@ -1309,19 +1321,19 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>10</v>
@@ -1332,16 +1344,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>69</v>
@@ -1355,7 +1367,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>70</v>
@@ -1364,7 +1376,7 @@
         <v>23</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>71</v>
@@ -1378,7 +1390,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>72</v>
@@ -1387,7 +1399,7 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>73</v>
@@ -1401,16 +1413,16 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>75</v>
@@ -1424,7 +1436,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>76</v>
@@ -1433,7 +1445,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>77</v>
@@ -1447,7 +1459,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>78</v>
@@ -1456,7 +1468,7 @@
         <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>79</v>
@@ -1470,7 +1482,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>80</v>
@@ -1479,7 +1491,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>81</v>
@@ -1493,7 +1505,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>82</v>
@@ -1502,7 +1514,7 @@
         <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>83</v>
@@ -1516,7 +1528,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>84</v>
@@ -1525,7 +1537,7 @@
         <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>85</v>
@@ -1539,7 +1551,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>86</v>
@@ -1548,7 +1560,7 @@
         <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>87</v>
@@ -1562,7 +1574,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>88</v>
@@ -1571,7 +1583,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>89</v>
@@ -1585,19 +1597,19 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -1608,19 +1620,19 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
@@ -1631,16 +1643,16 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>94</v>
@@ -1654,7 +1666,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>95</v>
@@ -1663,7 +1675,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>96</v>
@@ -1677,7 +1689,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>97</v>
@@ -1686,7 +1698,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>98</v>
@@ -1700,7 +1712,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>99</v>
@@ -1709,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>100</v>
@@ -1723,7 +1735,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>101</v>
@@ -1732,7 +1744,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>102</v>
@@ -1746,7 +1758,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>103</v>
@@ -1755,7 +1767,7 @@
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>104</v>
@@ -1769,7 +1781,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>105</v>
@@ -1778,7 +1790,7 @@
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>106</v>
@@ -1792,7 +1804,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>107</v>
@@ -1801,7 +1813,7 @@
         <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>108</v>
@@ -1815,7 +1827,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>109</v>
@@ -1824,7 +1836,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>110</v>
@@ -1838,7 +1850,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>111</v>
@@ -1847,7 +1859,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>112</v>
@@ -1861,16 +1873,16 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>114</v>
@@ -1884,16 +1896,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>116</v>
@@ -1907,7 +1919,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>117</v>
@@ -1916,7 +1928,7 @@
         <v>23</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>118</v>
@@ -1930,16 +1942,16 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>120</v>
@@ -1953,16 +1965,16 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>122</v>
@@ -1976,7 +1988,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>123</v>
@@ -1985,7 +1997,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>124</v>
@@ -1999,7 +2011,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>125</v>
@@ -2008,7 +2020,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>126</v>
@@ -2022,7 +2034,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>127</v>
@@ -2031,7 +2043,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>128</v>
@@ -2045,7 +2057,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>129</v>
@@ -2054,7 +2066,7 @@
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>130</v>
@@ -2068,19 +2080,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2091,19 +2103,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>131</v>
+        <v>66</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2114,16 +2126,16 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>69</v>
@@ -2137,7 +2149,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>70</v>
@@ -2146,7 +2158,7 @@
         <v>23</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>71</v>
@@ -2160,7 +2172,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>72</v>
@@ -2169,7 +2181,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>73</v>
@@ -2183,16 +2195,16 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>75</v>
@@ -2206,7 +2218,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>76</v>
@@ -2215,7 +2227,7 @@
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>77</v>
@@ -2229,7 +2241,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>78</v>
@@ -2238,7 +2250,7 @@
         <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>79</v>
@@ -2252,7 +2264,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>80</v>
@@ -2261,7 +2273,7 @@
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>81</v>
@@ -2275,7 +2287,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>82</v>
@@ -2284,7 +2296,7 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>83</v>
@@ -2298,7 +2310,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>84</v>
@@ -2307,7 +2319,7 @@
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>85</v>
@@ -2321,7 +2333,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>86</v>
@@ -2330,7 +2342,7 @@
         <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>87</v>
@@ -2344,7 +2356,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>88</v>
@@ -2353,7 +2365,7 @@
         <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>89</v>
@@ -2367,19 +2379,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2390,19 +2402,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2413,16 +2425,16 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>94</v>
@@ -2436,7 +2448,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>95</v>
@@ -2445,7 +2457,7 @@
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>96</v>
@@ -2459,7 +2471,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>97</v>
@@ -2468,7 +2480,7 @@
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>98</v>
@@ -2482,7 +2494,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>99</v>
@@ -2491,7 +2503,7 @@
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>100</v>
@@ -2505,7 +2517,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>101</v>
@@ -2514,7 +2526,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>102</v>
@@ -2528,7 +2540,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>103</v>
@@ -2537,7 +2549,7 @@
         <v>9</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>104</v>
@@ -2551,7 +2563,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>105</v>
@@ -2560,7 +2572,7 @@
         <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>106</v>
@@ -2574,7 +2586,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>107</v>
@@ -2583,7 +2595,7 @@
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>108</v>
@@ -2597,7 +2609,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>109</v>
@@ -2606,7 +2618,7 @@
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>110</v>
@@ -2620,7 +2632,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>111</v>
@@ -2629,7 +2641,7 @@
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>112</v>
@@ -2643,16 +2655,16 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>114</v>
@@ -2666,16 +2678,16 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>116</v>
@@ -2689,7 +2701,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>117</v>
@@ -2698,7 +2710,7 @@
         <v>23</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>118</v>
@@ -2712,16 +2724,16 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>120</v>
@@ -2735,16 +2747,16 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>122</v>
@@ -2758,7 +2770,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>123</v>
@@ -2767,7 +2779,7 @@
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>124</v>
@@ -2781,7 +2793,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>125</v>
@@ -2790,7 +2802,7 @@
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>126</v>
@@ -2804,7 +2816,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>127</v>
@@ -2813,7 +2825,7 @@
         <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>128</v>
@@ -2827,7 +2839,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>129</v>
@@ -2836,7 +2848,7 @@
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>130</v>
@@ -2850,19 +2862,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2873,19 +2885,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="C98" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2896,16 +2908,16 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>140</v>
@@ -2919,7 +2931,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>141</v>
@@ -2928,7 +2940,7 @@
         <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>142</v>
@@ -2942,7 +2954,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>143</v>
@@ -2951,7 +2963,7 @@
         <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>144</v>
@@ -2965,7 +2977,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>145</v>
@@ -2974,7 +2986,7 @@
         <v>9</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>146</v>
@@ -2988,7 +3000,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>147</v>
@@ -2997,10 +3009,10 @@
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -3011,19 +3023,19 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -3034,19 +3046,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -3057,19 +3069,19 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -3080,19 +3092,19 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>154</v>
+        <v>31</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
@@ -3103,7 +3115,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>155</v>
@@ -3112,7 +3124,7 @@
         <v>9</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>156</v>
@@ -3126,7 +3138,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>157</v>
@@ -3135,7 +3147,7 @@
         <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>158</v>
@@ -3149,19 +3161,19 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="C110" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D110" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>10</v>
@@ -3172,19 +3184,19 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>10</v>
@@ -3195,16 +3207,16 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>140</v>
@@ -3218,7 +3230,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>141</v>
@@ -3227,7 +3239,7 @@
         <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>142</v>
@@ -3241,7 +3253,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>143</v>
@@ -3250,7 +3262,7 @@
         <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>144</v>
@@ -3264,7 +3276,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>145</v>
@@ -3273,7 +3285,7 @@
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>146</v>
@@ -3287,7 +3299,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>147</v>
@@ -3296,10 +3308,10 @@
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>10</v>
@@ -3310,19 +3322,19 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>10</v>
@@ -3333,19 +3345,19 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>10</v>
@@ -3356,19 +3368,19 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
@@ -3379,19 +3391,19 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>154</v>
+        <v>31</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>10</v>
@@ -3402,7 +3414,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>155</v>
@@ -3411,7 +3423,7 @@
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>156</v>
@@ -3425,7 +3437,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>157</v>
@@ -3434,7 +3446,7 @@
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>158</v>
@@ -3448,22 +3460,22 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>29</v>
@@ -3471,19 +3483,19 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C124" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>65</v>
+        <v>162</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
@@ -3494,22 +3506,22 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>67</v>
+        <v>168</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>29</v>
@@ -3517,16 +3529,16 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>69</v>
@@ -3540,22 +3552,22 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>71</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>29</v>
@@ -3563,7 +3575,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>72</v>
@@ -3572,7 +3584,7 @@
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>73</v>
@@ -3586,7 +3598,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>74</v>
@@ -3595,7 +3607,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>75</v>
@@ -3609,7 +3621,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>76</v>
@@ -3618,13 +3630,13 @@
         <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>77</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>29</v>
@@ -3632,22 +3644,22 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>29</v>
@@ -3655,22 +3667,22 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>81</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>29</v>
@@ -3678,16 +3690,16 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>83</v>
@@ -3701,22 +3713,22 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>29</v>
@@ -3724,7 +3736,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>86</v>
@@ -3733,7 +3745,7 @@
         <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>87</v>
@@ -3747,7 +3759,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>88</v>
@@ -3756,7 +3768,7 @@
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>89</v>
@@ -3770,22 +3782,22 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>29</v>
@@ -3793,22 +3805,22 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>29</v>
@@ -3816,22 +3828,22 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>94</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>29</v>
@@ -3839,22 +3851,22 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>29</v>
@@ -3862,22 +3874,22 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G141" s="2" t="s">
         <v>29</v>
@@ -3885,7 +3897,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>99</v>
@@ -3894,13 +3906,13 @@
         <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>100</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G142" s="2" t="s">
         <v>29</v>
@@ -3908,7 +3920,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>101</v>
@@ -3917,7 +3929,7 @@
         <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>102</v>
@@ -3931,7 +3943,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>103</v>
@@ -3940,7 +3952,7 @@
         <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>104</v>
@@ -3954,7 +3966,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>105</v>
@@ -3963,7 +3975,7 @@
         <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>106</v>
@@ -3977,7 +3989,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>107</v>
@@ -3986,7 +3998,7 @@
         <v>9</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>108</v>
@@ -4000,7 +4012,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>109</v>
@@ -4009,7 +4021,7 @@
         <v>9</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>110</v>
@@ -4023,7 +4035,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>111</v>
@@ -4032,13 +4044,13 @@
         <v>9</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>112</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>29</v>
@@ -4046,22 +4058,22 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>114</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G149" s="2" t="s">
         <v>29</v>
@@ -4069,22 +4081,22 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>116</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>29</v>
@@ -4092,22 +4104,22 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>165</v>
+        <v>117</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>118</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>29</v>
@@ -4115,19 +4127,19 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>10</v>
@@ -4138,22 +4150,22 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>29</v>
@@ -4161,16 +4173,16 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>173</v>
@@ -4184,7 +4196,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>174</v>
@@ -4193,7 +4205,7 @@
         <v>23</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>175</v>
@@ -4207,7 +4219,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>176</v>
@@ -4216,7 +4228,7 @@
         <v>23</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>177</v>
@@ -4230,16 +4242,16 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>179</v>
@@ -4253,16 +4265,16 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>181</v>
@@ -4276,7 +4288,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>182</v>
@@ -4285,7 +4297,7 @@
         <v>9</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>183</v>
@@ -4299,7 +4311,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>184</v>
@@ -4308,7 +4320,7 @@
         <v>9</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>185</v>
@@ -4322,24 +4334,70 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>53</v>
+        <v>186</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G161" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G163" s="2" t="s">
         <v>29</v>
       </c>
     </row>
